--- a/grupos/6ALCV - Estadisticos 20232.xlsx
+++ b/grupos/6ALCV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="76">
   <si>
     <t>Materia</t>
   </si>
@@ -191,12 +191,12 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
@@ -215,64 +215,37 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>VILLA</t>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>REYLI</t>
   </si>
   <si>
     <t>ALONDRA YURIDIA</t>
   </si>
   <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
     <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>FLOR GUADALUPE</t>
   </si>
 </sst>
 </file>
@@ -780,22 +753,22 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -816,19 +789,19 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>6</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -857,22 +830,22 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -893,19 +866,19 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>8</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -934,22 +907,22 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -970,7 +943,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>10</v>
@@ -1011,22 +984,22 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1047,22 +1020,22 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1088,22 +1061,22 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1133,7 +1106,7 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1165,22 +1138,22 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1201,19 +1174,19 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1242,22 +1215,22 @@
         <v>4</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1278,19 +1251,19 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1319,22 +1292,22 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1361,7 +1334,7 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1396,22 +1369,22 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1432,7 +1405,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>5</v>
@@ -1473,22 +1446,22 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1515,10 +1488,10 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1550,22 +1523,22 @@
         <v>4</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1586,10 +1559,10 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1627,22 +1600,22 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1704,22 +1677,22 @@
         <v>4</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1740,7 +1713,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>8</v>
@@ -1781,22 +1754,22 @@
         <v>4</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1820,7 +1793,7 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -1858,22 +1831,22 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1900,10 +1873,10 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -1935,22 +1908,22 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1986,7 +1959,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2012,22 +1985,22 @@
         <v>7</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2051,19 +2024,19 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2089,22 +2062,22 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2125,19 +2098,19 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>6</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2166,22 +2139,22 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2205,7 +2178,7 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2243,22 +2216,22 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2282,19 +2255,19 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>6</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2320,22 +2293,22 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2359,13 +2332,13 @@
         <v>8</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>10</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2397,22 +2370,22 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2433,16 +2406,16 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2474,22 +2447,22 @@
         <v>9</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2513,16 +2486,16 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>10</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2551,22 +2524,22 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2593,16 +2566,16 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2628,22 +2601,22 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2667,19 +2640,19 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>5</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2705,22 +2678,22 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2747,10 +2720,10 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -2782,22 +2755,22 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2821,7 +2794,7 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>10</v>
@@ -2830,7 +2803,7 @@
         <v>7</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -2859,22 +2832,22 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2907,10 +2880,10 @@
         <v>6</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2936,22 +2909,22 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -2975,19 +2948,19 @@
         <v>8</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3013,22 +2986,22 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3049,22 +3022,22 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>5</v>
       </c>
       <c r="V33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>5</v>
       </c>
       <c r="X33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3090,22 +3063,22 @@
         <v>4</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3132,13 +3105,13 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>5</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>5</v>
@@ -3167,22 +3140,22 @@
         <v>9</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3209,10 +3182,10 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3369,7 +3342,7 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
       <c r="N4">
         <v>100</v>
@@ -3387,7 +3360,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3413,7 +3386,7 @@
         <v>93.3</v>
       </c>
       <c r="H5">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -3428,10 +3401,10 @@
         <v>100</v>
       </c>
       <c r="M5">
-        <v>93.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N5">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -3446,7 +3419,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>93.3</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3487,7 +3460,7 @@
         <v>100</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="N6">
         <v>100</v>
@@ -3505,7 +3478,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3531,7 +3504,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="I7">
         <v>100</v>
@@ -3546,10 +3519,10 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -3564,7 +3537,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3664,7 +3637,7 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N9">
         <v>100</v>
@@ -3682,7 +3655,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3723,7 +3696,7 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>76.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N10">
         <v>100</v>
@@ -3741,7 +3714,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>76.7</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3782,7 +3755,7 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="N11">
         <v>100</v>
@@ -3800,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3826,7 +3799,7 @@
         <v>93.3</v>
       </c>
       <c r="H12">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -3841,10 +3814,10 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>93.3</v>
+        <v>94.5</v>
       </c>
       <c r="N12">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -3859,7 +3832,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>93.3</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3953,31 +3926,31 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L14">
         <v>100</v>
       </c>
       <c r="M14">
+        <v>85.5</v>
+      </c>
+      <c r="N14">
+        <v>100</v>
+      </c>
+      <c r="O14">
+        <v>100</v>
+      </c>
+      <c r="P14">
+        <v>100</v>
+      </c>
+      <c r="Q14">
         <v>90</v>
       </c>
-      <c r="N14">
-        <v>100</v>
-      </c>
-      <c r="O14">
-        <v>100</v>
-      </c>
-      <c r="P14">
-        <v>100</v>
-      </c>
-      <c r="Q14">
-        <v>80</v>
-      </c>
       <c r="R14">
         <v>100</v>
       </c>
       <c r="S14">
-        <v>90</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4077,7 +4050,7 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>66.7</v>
+        <v>78.2</v>
       </c>
       <c r="N16">
         <v>87.5</v>
@@ -4095,7 +4068,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>66.7</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4121,7 +4094,7 @@
         <v>66.7</v>
       </c>
       <c r="H17">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="I17">
         <v>100</v>
@@ -4136,10 +4109,10 @@
         <v>100</v>
       </c>
       <c r="M17">
-        <v>66.7</v>
+        <v>78.2</v>
       </c>
       <c r="N17">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -4154,7 +4127,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>66.7</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4195,7 +4168,7 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N18">
         <v>100</v>
@@ -4213,7 +4186,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4254,7 +4227,7 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>93.3</v>
+        <v>94.5</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -4272,7 +4245,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>93.3</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4313,7 +4286,7 @@
         <v>100</v>
       </c>
       <c r="M20">
-        <v>93.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N20">
         <v>100</v>
@@ -4331,7 +4304,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>93.3</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4357,7 +4330,7 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="I21">
         <v>100</v>
@@ -4372,10 +4345,10 @@
         <v>100</v>
       </c>
       <c r="M21">
-        <v>100</v>
+        <v>92.7</v>
       </c>
       <c r="N21">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -4390,7 +4363,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4431,7 +4404,7 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N22">
         <v>100</v>
@@ -4449,7 +4422,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4490,7 +4463,7 @@
         <v>100</v>
       </c>
       <c r="M23">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -4508,7 +4481,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4549,7 +4522,7 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="N24">
         <v>100</v>
@@ -4567,7 +4540,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4608,7 +4581,7 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="N25">
         <v>100</v>
@@ -4626,7 +4599,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4667,7 +4640,7 @@
         <v>100</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N26">
         <v>100</v>
@@ -4685,7 +4658,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4726,7 +4699,7 @@
         <v>100</v>
       </c>
       <c r="M27">
-        <v>100</v>
+        <v>92.7</v>
       </c>
       <c r="N27">
         <v>100</v>
@@ -4744,7 +4717,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4785,7 +4758,7 @@
         <v>100</v>
       </c>
       <c r="M28">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N28">
         <v>100</v>
@@ -4803,7 +4776,7 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4903,7 +4876,7 @@
         <v>100</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="N30">
         <v>100</v>
@@ -4921,7 +4894,7 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>100</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4962,7 +4935,7 @@
         <v>100</v>
       </c>
       <c r="M31">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="N31">
         <v>100</v>
@@ -4980,7 +4953,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>100</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5021,7 +4994,7 @@
         <v>100</v>
       </c>
       <c r="M32">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N32">
         <v>100</v>
@@ -5039,7 +5012,7 @@
         <v>100</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5080,7 +5053,7 @@
         <v>100</v>
       </c>
       <c r="M33">
-        <v>100</v>
+        <v>87.3</v>
       </c>
       <c r="N33">
         <v>100</v>
@@ -5098,7 +5071,7 @@
         <v>100</v>
       </c>
       <c r="S33">
-        <v>100</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5133,13 +5106,13 @@
         <v>100</v>
       </c>
       <c r="K34">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="L34">
         <v>100</v>
       </c>
       <c r="M34">
-        <v>76.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N34">
         <v>75</v>
@@ -5151,13 +5124,13 @@
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="R34">
         <v>100</v>
       </c>
       <c r="S34">
-        <v>76.7</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5198,7 +5171,7 @@
         <v>100</v>
       </c>
       <c r="M35">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N35">
         <v>100</v>
@@ -5216,7 +5189,7 @@
         <v>100</v>
       </c>
       <c r="S35">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -5282,19 +5255,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2">
-        <v>71.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="G2" s="2">
-        <v>28.1</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5305,7 +5278,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -5314,19 +5287,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>71.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="G3" s="2">
-        <v>28.1</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5337,7 +5310,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -5358,7 +5331,7 @@
         <v>21.9</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5372,25 +5345,25 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C5">
         <v>32</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>81.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>18.8</v>
+        <v>15.6</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5410,19 +5383,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5442,19 +5415,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5504,7 +5477,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5536,22 +5509,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920100</v>
+        <v>21330051920107</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" t="s">
         <v>72</v>
       </c>
-      <c r="D2" t="s">
-        <v>78</v>
-      </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5559,22 +5532,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920100</v>
+        <v>21330051920107</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
       </c>
       <c r="C3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" t="s">
         <v>72</v>
       </c>
-      <c r="D3" t="s">
-        <v>78</v>
-      </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5582,19 +5555,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920191</v>
+        <v>20330051920378</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" t="s">
         <v>73</v>
       </c>
-      <c r="D4" t="s">
-        <v>79</v>
-      </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>58</v>
@@ -5605,16 +5578,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920071</v>
+        <v>21330051920100</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" t="s">
         <v>74</v>
-      </c>
-      <c r="D5" t="s">
-        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -5628,7 +5601,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920075</v>
+        <v>21330051920102</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -5637,84 +5610,15 @@
         <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920302</v>
-      </c>
-      <c r="B7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920102</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920387</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ALCV - Estadisticos 20232.xlsx
+++ b/grupos/6ALCV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="84">
   <si>
     <t>Materia</t>
   </si>
@@ -188,21 +188,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Reyes Cruz Eder Yaveth</t>
+  </si>
+  <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
-    <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
-    <t>Reyes Cruz Eder Yaveth</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -215,37 +215,61 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -771,22 +795,22 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -795,16 +819,16 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>6</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -848,25 +872,25 @@
         <v>4</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>6</v>
@@ -875,10 +899,10 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -925,22 +949,22 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1002,22 +1026,22 @@
         <v>4</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1026,13 +1050,13 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1070,7 +1094,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -1079,25 +1103,25 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1156,40 +1180,40 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1233,22 +1257,22 @@
         <v>4</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1257,13 +1281,13 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>7</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1310,22 +1334,22 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1343,7 +1367,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1387,40 +1411,40 @@
         <v>4</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>7</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1464,22 +1488,22 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1491,13 +1515,13 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1541,37 +1565,37 @@
         <v>4</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1618,22 +1642,22 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1695,37 +1719,37 @@
         <v>4</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="T16">
         <v>6</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1772,37 +1796,37 @@
         <v>4</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>6</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -1849,22 +1873,22 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -1876,13 +1900,13 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1926,22 +1950,22 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -1959,7 +1983,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2003,22 +2027,22 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2036,7 +2060,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2080,31 +2104,31 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>7</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2113,7 +2137,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2157,22 +2181,22 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2190,7 +2214,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2234,31 +2258,31 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>7</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -2311,25 +2335,25 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2338,7 +2362,7 @@
         <v>10</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2388,22 +2412,22 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2421,7 +2445,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2465,22 +2489,22 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>8</v>
@@ -2492,13 +2516,13 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2542,22 +2566,22 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -2575,7 +2599,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2619,40 +2643,40 @@
         <v>4</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>6</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>6</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2693,25 +2717,25 @@
         <v>10</v>
       </c>
       <c r="M29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -2773,22 +2797,22 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -2850,31 +2874,31 @@
         <v>4</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U31">
         <v>6</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -2883,7 +2907,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2927,22 +2951,22 @@
         <v>4</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
         <v>8</v>
@@ -3004,37 +3028,37 @@
         <v>4</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>6</v>
@@ -3081,37 +3105,37 @@
         <v>4</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T34">
         <v>6</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>5</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>5</v>
@@ -3158,22 +3182,22 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T35">
         <v>8</v>
@@ -3188,10 +3212,10 @@
         <v>6</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3345,7 +3369,7 @@
         <v>94.5</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -3360,7 +3384,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3404,7 +3428,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="N5">
-        <v>93.8</v>
+        <v>89.8</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -3419,7 +3443,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>89.09999999999999</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3478,7 +3502,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3522,7 +3546,7 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N7">
-        <v>87.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -3537,7 +3561,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3640,10 +3664,10 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>70.3</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3655,7 +3679,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3714,7 +3738,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>83.59999999999999</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3773,7 +3797,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3817,7 +3841,7 @@
         <v>94.5</v>
       </c>
       <c r="N12">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -3832,7 +3856,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3944,13 +3968,13 @@
         <v>100</v>
       </c>
       <c r="Q14">
+        <v>81.3</v>
+      </c>
+      <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
         <v>90</v>
-      </c>
-      <c r="R14">
-        <v>100</v>
-      </c>
-      <c r="S14">
-        <v>85.5</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4053,7 +4077,7 @@
         <v>78.2</v>
       </c>
       <c r="N16">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -4068,7 +4092,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>78.2</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4112,7 +4136,7 @@
         <v>78.2</v>
       </c>
       <c r="N17">
-        <v>93.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -4127,7 +4151,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>78.2</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4186,7 +4210,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4245,7 +4269,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4304,7 +4328,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4348,7 +4372,7 @@
         <v>92.7</v>
       </c>
       <c r="N21">
-        <v>93.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -4363,7 +4387,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>92.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4422,7 +4446,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4481,7 +4505,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4540,7 +4564,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4599,7 +4623,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4658,7 +4682,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4717,7 +4741,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>92.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4776,7 +4800,7 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4894,7 +4918,7 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4953,7 +4977,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5012,7 +5036,7 @@
         <v>100</v>
       </c>
       <c r="S32">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5071,7 +5095,7 @@
         <v>100</v>
       </c>
       <c r="S33">
-        <v>87.3</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5115,7 +5139,7 @@
         <v>69.09999999999999</v>
       </c>
       <c r="N34">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -5124,13 +5148,13 @@
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>86</v>
+        <v>78.8</v>
       </c>
       <c r="R34">
         <v>100</v>
       </c>
       <c r="S34">
-        <v>69.09999999999999</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5189,7 +5213,7 @@
         <v>100</v>
       </c>
       <c r="S35">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
   </sheetData>
@@ -5246,7 +5270,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -5267,7 +5291,7 @@
         <v>25</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5278,7 +5302,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -5287,19 +5311,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>75</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>25</v>
+        <v>3.1</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5310,7 +5334,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -5319,19 +5343,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>78.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>21.9</v>
+        <v>3.1</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5342,28 +5366,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5">
         <v>32</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>84.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>15.6</v>
+        <v>3.1</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5374,28 +5398,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6">
         <v>32</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>90.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5406,7 +5430,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
@@ -5415,19 +5439,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5477,7 +5501,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5509,19 +5533,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920107</v>
+        <v>21330051920109</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>59</v>
@@ -5532,19 +5556,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920107</v>
+        <v>21330051920109</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>56</v>
@@ -5555,22 +5579,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920378</v>
+        <v>20330051920191</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5578,19 +5602,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920100</v>
+        <v>21330051920071</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>56</v>
@@ -5601,7 +5625,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920102</v>
+        <v>21330051920075</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -5610,15 +5634,84 @@
         <v>66</v>
       </c>
       <c r="D6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920078</v>
+      </c>
+      <c r="B7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920260</v>
+      </c>
+      <c r="B8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" t="s">
         <v>75</v>
       </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6">
+      <c r="D8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920080</v>
+      </c>
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
     </row>
